--- a/npc/doc/NPC性能评估结果.xlsx
+++ b/npc/doc/NPC性能评估结果.xlsx
@@ -255,7 +255,7 @@
     <t xml:space="preserve">将icache改为4块，每块大小16B，并测试其性能。测试16B块大小的icache性能，得到命中率为90.55%，与仿真结果90.52%非常接近。同时相比之前的命中率有所提高。AMAT为21.27，尽管命中率提高，但因为没有突发传输导致缺失代价大幅上升，导致其增加。出现了性能倒退，分析后得出其原因是icache访问存储器的时间增加导致了IFU等待周期大幅上升，因为块的大小大于单条指令大小必定会取一切没用到的指令。但是目前没有实现突发传输，实现突发传输之后肯定会有所改善。</t>
   </si>
   <si>
-    <t xml:space="preserve">当前commit</t>
+    <t xml:space="preserve">39d24b88c32bc880a5a0f5cdce75c890de6b8fd8</t>
   </si>
   <si>
     <t xml:space="preserve">将icache改为了突发传输，IPS再次有所提升，提升主要来源于AMAT的下降</t>

--- a/npc/doc/NPC性能评估结果.xlsx
+++ b/npc/doc/NPC性能评估结果.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="81">
   <si>
     <t xml:space="preserve">commit</t>
   </si>
@@ -38,6 +38,9 @@
   </si>
   <si>
     <t xml:space="preserve">综合频率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPS</t>
   </si>
   <si>
     <t xml:space="preserve">综合面积</t>
@@ -259,6 +262,12 @@
   </si>
   <si>
     <t xml:space="preserve">将icache改为了突发传输，IPS再次有所提升，提升主要来源于AMAT的下降</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当前commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过为编译器添加参数控制函数与跳转位置来对程序进行适配优化，使其性能稍有提升</t>
   </si>
 </sst>
 </file>
@@ -403,8 +412,8 @@
     <tabColor rgb="FF000000"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:CX1048576"/>
-  <sheetFormatPr defaultColWidth="13.4765625" defaultRowHeight="18" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:CY1048576"/>
+  <sheetFormatPr defaultColWidth="13.4609375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.03"/>
   </cols>
@@ -434,7 +443,9 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
@@ -443,30 +454,30 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
-      <c r="R1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="T1" s="2"/>
       <c r="U1" s="2"/>
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
-      <c r="Z1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA1" s="2"/>
+      <c r="Z1" s="2"/>
+      <c r="AA1" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="AB1" s="2"/>
       <c r="AC1" s="2"/>
       <c r="AD1" s="2"/>
       <c r="AE1" s="2"/>
       <c r="AF1" s="2"/>
       <c r="AG1" s="2"/>
-      <c r="AH1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI1" s="2"/>
+      <c r="AH1" s="2"/>
+      <c r="AI1" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
       <c r="AL1" s="2"/>
@@ -480,18 +491,18 @@
       <c r="AT1" s="2"/>
       <c r="AU1" s="2"/>
       <c r="AV1" s="2"/>
-      <c r="AW1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="AX1" s="2"/>
+      <c r="AW1" s="2"/>
+      <c r="AX1" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="AY1" s="2"/>
       <c r="AZ1" s="2"/>
       <c r="BA1" s="2"/>
       <c r="BB1" s="2"/>
-      <c r="BC1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="BD1" s="2"/>
+      <c r="BC1" s="2"/>
+      <c r="BD1" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="BE1" s="2"/>
       <c r="BF1" s="2"/>
       <c r="BG1" s="2"/>
@@ -499,10 +510,10 @@
       <c r="BI1" s="2"/>
       <c r="BJ1" s="2"/>
       <c r="BK1" s="2"/>
-      <c r="BL1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="BM1" s="2"/>
+      <c r="BL1" s="2"/>
+      <c r="BM1" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="BN1" s="2"/>
       <c r="BO1" s="2"/>
       <c r="BP1" s="2"/>
@@ -532,18 +543,19 @@
       <c r="CN1" s="2"/>
       <c r="CO1" s="2"/>
       <c r="CP1" s="2"/>
-      <c r="CQ1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="CR1" s="2"/>
-      <c r="CS1" s="3" t="s">
+      <c r="CQ1" s="2"/>
+      <c r="CR1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="CT1" s="3"/>
+      <c r="CS1" s="2"/>
+      <c r="CT1" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="CU1" s="3"/>
       <c r="CV1" s="3"/>
       <c r="CW1" s="3"/>
       <c r="CX1" s="3"/>
+      <c r="CY1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2"/>
@@ -553,13 +565,13 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="2"/>
+      <c r="J2" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
@@ -567,40 +579,40 @@
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
-      <c r="R2" s="2" t="s">
-        <v>18</v>
-      </c>
+      <c r="R2" s="2"/>
       <c r="S2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="2"/>
+      <c r="T2" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="U2" s="2"/>
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
       <c r="X2" s="2"/>
       <c r="Y2" s="2"/>
-      <c r="Z2" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="Z2" s="2"/>
       <c r="AA2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AB2" s="2"/>
+      <c r="AB2" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="AC2" s="2"/>
       <c r="AD2" s="2"/>
       <c r="AE2" s="2"/>
       <c r="AF2" s="2"/>
       <c r="AG2" s="2"/>
-      <c r="AH2" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="AH2" s="2"/>
       <c r="AI2" s="2" t="s">
         <v>23</v>
       </c>
       <c r="AJ2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AK2" s="2"/>
+      <c r="AK2" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="AL2" s="2"/>
       <c r="AM2" s="2"/>
       <c r="AN2" s="2"/>
@@ -612,19 +624,17 @@
       <c r="AT2" s="2"/>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
-      <c r="AW2" s="2" t="s">
+      <c r="AW2" s="2"/>
+      <c r="AX2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AY2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AX2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="AY2" s="2"/>
       <c r="AZ2" s="2"/>
       <c r="BA2" s="2"/>
       <c r="BB2" s="2"/>
-      <c r="BC2" s="4" t="s">
-        <v>26</v>
-      </c>
+      <c r="BC2" s="2"/>
       <c r="BD2" s="4" t="s">
         <v>27</v>
       </c>
@@ -637,7 +647,7 @@
       <c r="BG2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="BH2" s="2" t="s">
+      <c r="BH2" s="4" t="s">
         <v>31</v>
       </c>
       <c r="BI2" s="2" t="s">
@@ -652,103 +662,103 @@
       <c r="BL2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="BM2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="BN2" s="3" t="s">
+      <c r="BM2" s="2" t="s">
         <v>36</v>
+      </c>
+      <c r="BN2" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="BO2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="BP2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="BQ2" s="3" t="s">
-        <v>36</v>
+      <c r="BP2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="BQ2" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="BR2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="BS2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="BT2" s="3" t="s">
-        <v>36</v>
+      <c r="BS2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="BT2" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="BU2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="BV2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="BW2" s="3" t="s">
-        <v>36</v>
+      <c r="BV2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="BW2" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="BX2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="BY2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="BZ2" s="3" t="s">
-        <v>36</v>
+      <c r="BY2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="BZ2" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="CA2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="CB2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="CC2" s="3" t="s">
-        <v>36</v>
+      <c r="CB2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="CC2" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="CD2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="CE2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="CF2" s="3" t="s">
-        <v>36</v>
+      <c r="CE2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="CF2" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="CG2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="CH2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="CI2" s="3" t="s">
-        <v>36</v>
+      <c r="CH2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="CI2" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="CJ2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="CK2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="CL2" s="3" t="s">
-        <v>36</v>
+      <c r="CK2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="CL2" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="CM2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="CN2" s="2" t="s">
+      <c r="CN2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="CO2" s="3" t="s">
-        <v>36</v>
+      <c r="CO2" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="CP2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="CQ2" s="5" t="s">
-        <v>39</v>
+      <c r="CQ2" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="CR2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="CS2" s="6" t="s">
+      <c r="CS2" s="5" t="s">
         <v>41</v>
       </c>
       <c r="CT2" s="6" t="s">
@@ -765,6 +775,9 @@
       </c>
       <c r="CX2" s="6" t="s">
         <v>46</v>
+      </c>
+      <c r="CY2" s="6" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -776,135 +789,135 @@
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-      <c r="I3" s="7" t="s">
-        <v>47</v>
-      </c>
+      <c r="I3" s="2"/>
       <c r="J3" s="7" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="R3" s="2"/>
-      <c r="S3" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R3" s="7" t="s">
         <v>52</v>
       </c>
+      <c r="S3" s="2"/>
       <c r="T3" s="7" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="U3" s="7" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="V3" s="7" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="W3" s="7" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="X3" s="7" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="Y3" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z3" s="2"/>
-      <c r="AA3" s="7" t="s">
-        <v>55</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="Z3" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA3" s="2"/>
       <c r="AB3" s="7" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="AC3" s="7" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="AD3" s="7" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="AE3" s="7" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="AF3" s="7" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="AG3" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="AH3" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="AH3" s="7" t="s">
+        <v>52</v>
+      </c>
       <c r="AI3" s="2"/>
-      <c r="AJ3" s="7" t="s">
-        <v>58</v>
-      </c>
+      <c r="AJ3" s="2"/>
       <c r="AK3" s="7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="AL3" s="7" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="AM3" s="7" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AN3" s="7" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="AO3" s="7" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="AP3" s="7" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="AQ3" s="7" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="AR3" s="7" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="AS3" s="7" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="AT3" s="7" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="AU3" s="7" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="AV3" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="AW3" s="2"/>
-      <c r="AX3" s="7" t="s">
-        <v>64</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="AW3" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AX3" s="2"/>
       <c r="AY3" s="7" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AZ3" s="7" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="BA3" s="7" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="BB3" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="BC3" s="4"/>
+        <v>37</v>
+      </c>
+      <c r="BC3" s="7" t="s">
+        <v>52</v>
+      </c>
       <c r="BD3" s="4"/>
       <c r="BE3" s="4"/>
       <c r="BF3" s="4"/>
@@ -944,25 +957,26 @@
       <c r="CN3" s="4"/>
       <c r="CO3" s="4"/>
       <c r="CP3" s="4"/>
-      <c r="CQ3" s="5" t="s">
-        <v>66</v>
-      </c>
+      <c r="CQ3" s="4"/>
       <c r="CR3" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="CS3" s="6"/>
+        <v>67</v>
+      </c>
+      <c r="CS3" s="5" t="s">
+        <v>67</v>
+      </c>
       <c r="CT3" s="6"/>
       <c r="CU3" s="6"/>
       <c r="CV3" s="6"/>
       <c r="CW3" s="6"/>
       <c r="CX3" s="6"/>
+      <c r="CY3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="88.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>10249068096</v>
@@ -977,247 +991,247 @@
         <v>727.908</v>
       </c>
       <c r="G4" s="1" t="n">
+        <v>13830252</v>
+      </c>
+      <c r="H4" s="1" t="n">
         <v>13235.096</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="I4" s="1" t="n">
         <v>195179616</v>
       </c>
-      <c r="I4" s="1" t="n">
+      <c r="J4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="K4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="1" t="n">
+      <c r="L4" s="1" t="n">
         <v>8838413966</v>
       </c>
-      <c r="L4" s="1" t="n">
+      <c r="M4" s="1" t="n">
         <v>86.24</v>
       </c>
-      <c r="M4" s="1" t="n">
+      <c r="N4" s="1" t="n">
         <v>195179616</v>
       </c>
-      <c r="N4" s="1" t="n">
+      <c r="O4" s="1" t="n">
         <v>1.9</v>
       </c>
-      <c r="O4" s="1" t="n">
+      <c r="P4" s="1" t="n">
         <v>1215474512</v>
       </c>
-      <c r="P4" s="1" t="n">
+      <c r="Q4" s="1" t="n">
         <v>11.86</v>
       </c>
-      <c r="R4" s="1" t="n">
+      <c r="S4" s="1" t="n">
         <v>195179616</v>
       </c>
-      <c r="S4" s="1" t="n">
+      <c r="T4" s="1" t="n">
         <v>8838413968</v>
       </c>
-      <c r="T4" s="1" t="n">
+      <c r="U4" s="1" t="n">
         <v>86.24</v>
       </c>
-      <c r="U4" s="1" t="n">
+      <c r="V4" s="1" t="n">
         <v>195179616</v>
       </c>
-      <c r="V4" s="1" t="n">
+      <c r="W4" s="1" t="n">
         <v>1.9</v>
       </c>
-      <c r="W4" s="1" t="n">
+      <c r="X4" s="1" t="n">
         <v>1215474512</v>
       </c>
-      <c r="X4" s="1" t="n">
+      <c r="Y4" s="1" t="n">
         <v>11.86</v>
       </c>
-      <c r="Z4" s="1" t="n">
+      <c r="AA4" s="1" t="n">
         <v>195179616</v>
       </c>
-      <c r="AA4" s="1" t="n">
+      <c r="AB4" s="1" t="n">
         <v>9033593584</v>
       </c>
-      <c r="AB4" s="1" t="n">
+      <c r="AC4" s="1" t="n">
         <v>88.14</v>
       </c>
-      <c r="AC4" s="1" t="n">
+      <c r="AD4" s="1" t="n">
         <v>195179616</v>
       </c>
-      <c r="AD4" s="1" t="n">
+      <c r="AE4" s="1" t="n">
         <v>1.9</v>
       </c>
-      <c r="AE4" s="1" t="n">
+      <c r="AF4" s="1" t="n">
         <v>1020294896</v>
       </c>
-      <c r="AF4" s="1" t="n">
+      <c r="AG4" s="1" t="n">
         <v>9.96</v>
       </c>
-      <c r="AH4" s="1" t="n">
+      <c r="AI4" s="1" t="n">
         <v>15597897</v>
       </c>
-      <c r="AI4" s="1" t="n">
+      <c r="AJ4" s="1" t="n">
         <v>7154860</v>
       </c>
-      <c r="AJ4" s="1" t="n">
+      <c r="AK4" s="1" t="n">
         <v>9251525958</v>
       </c>
-      <c r="AK4" s="1" t="n">
+      <c r="AL4" s="1" t="n">
         <v>90.27</v>
       </c>
-      <c r="AL4" s="1" t="n">
+      <c r="AM4" s="1" t="n">
         <v>624853786</v>
       </c>
-      <c r="AM4" s="1" t="n">
+      <c r="AN4" s="1" t="n">
         <v>6.1</v>
       </c>
-      <c r="AN4" s="1" t="n">
+      <c r="AO4" s="1" t="n">
         <v>15597897</v>
       </c>
-      <c r="AO4" s="1" t="n">
+      <c r="AP4" s="1" t="n">
         <v>0.15</v>
       </c>
-      <c r="AP4" s="1" t="n">
+      <c r="AQ4" s="1" t="n">
         <v>154755980</v>
       </c>
-      <c r="AQ4" s="1" t="n">
+      <c r="AR4" s="1" t="n">
         <v>1.51</v>
       </c>
-      <c r="AR4" s="1" t="n">
+      <c r="AS4" s="1" t="n">
         <v>7154860</v>
       </c>
-      <c r="AS4" s="1" t="n">
+      <c r="AT4" s="1" t="n">
         <v>0.07</v>
       </c>
-      <c r="AT4" s="1" t="n">
+      <c r="AU4" s="1" t="n">
         <v>195179615</v>
       </c>
-      <c r="AU4" s="1" t="n">
+      <c r="AV4" s="1" t="n">
         <v>1.9</v>
       </c>
-      <c r="AW4" s="1" t="n">
+      <c r="AX4" s="1" t="n">
         <v>195179616</v>
       </c>
-      <c r="AX4" s="1" t="n">
+      <c r="AY4" s="1" t="n">
         <v>10053888480</v>
       </c>
-      <c r="AY4" s="1" t="n">
+      <c r="AZ4" s="1" t="n">
         <v>98.1</v>
       </c>
-      <c r="AZ4" s="1" t="n">
+      <c r="BA4" s="1" t="n">
         <v>195179616</v>
       </c>
-      <c r="BA4" s="1" t="n">
+      <c r="BB4" s="1" t="n">
         <v>1.9</v>
       </c>
-      <c r="BC4" s="1" t="n">
+      <c r="BD4" s="1" t="n">
         <v>1577524</v>
       </c>
-      <c r="BD4" s="1" t="n">
+      <c r="BE4" s="1" t="n">
         <v>1928723</v>
       </c>
-      <c r="BE4" s="1" t="n">
+      <c r="BF4" s="1" t="n">
         <v>2032838</v>
       </c>
-      <c r="BF4" s="1" t="n">
+      <c r="BG4" s="1" t="n">
         <v>88301344</v>
       </c>
-      <c r="BG4" s="1" t="n">
+      <c r="BH4" s="1" t="n">
         <v>52598631</v>
       </c>
-      <c r="BH4" s="1" t="n">
+      <c r="BI4" s="1" t="n">
         <v>25987797</v>
       </c>
-      <c r="BI4" s="1" t="n">
+      <c r="BJ4" s="1" t="n">
         <v>15597897</v>
       </c>
-      <c r="BJ4" s="1" t="n">
+      <c r="BK4" s="1" t="n">
         <v>7154860</v>
       </c>
-      <c r="BK4" s="1" t="n">
+      <c r="BL4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="BL4" s="1" t="n">
+      <c r="BM4" s="1" t="n">
         <v>10249068096</v>
       </c>
-      <c r="BM4" s="1" t="n">
+      <c r="BN4" s="1" t="n">
         <v>89933678</v>
       </c>
-      <c r="BN4" s="1" t="n">
+      <c r="BO4" s="1" t="n">
         <v>0.88</v>
       </c>
-      <c r="BO4" s="1" t="n">
+      <c r="BP4" s="1" t="n">
         <v>57.01</v>
       </c>
-      <c r="BP4" s="1" t="n">
+      <c r="BQ4" s="1" t="n">
         <v>90409244</v>
       </c>
-      <c r="BQ4" s="1" t="n">
+      <c r="BR4" s="1" t="n">
         <v>0.88</v>
       </c>
-      <c r="BR4" s="1" t="n">
+      <c r="BS4" s="1" t="n">
         <v>46.88</v>
       </c>
-      <c r="BS4" s="1" t="n">
+      <c r="BT4" s="1" t="n">
         <v>97021159</v>
       </c>
-      <c r="BT4" s="1" t="n">
+      <c r="BU4" s="1" t="n">
         <v>0.95</v>
       </c>
-      <c r="BU4" s="1" t="n">
+      <c r="BV4" s="1" t="n">
         <v>47.73</v>
       </c>
-      <c r="BV4" s="1" t="n">
+      <c r="BW4" s="1" t="n">
         <v>4259224237</v>
       </c>
-      <c r="BW4" s="1" t="n">
+      <c r="BX4" s="1" t="n">
         <v>41.56</v>
       </c>
-      <c r="BX4" s="1" t="n">
+      <c r="BY4" s="1" t="n">
         <v>48.24</v>
       </c>
-      <c r="BY4" s="1" t="n">
+      <c r="BZ4" s="1" t="n">
         <v>2495938854</v>
       </c>
-      <c r="BZ4" s="1" t="n">
+      <c r="CA4" s="1" t="n">
         <v>24.35</v>
       </c>
-      <c r="CA4" s="1" t="n">
+      <c r="CB4" s="1" t="n">
         <v>47.45</v>
       </c>
-      <c r="CB4" s="1" t="n">
+      <c r="CC4" s="1" t="n">
         <v>1263483030</v>
       </c>
-      <c r="CC4" s="1" t="n">
+      <c r="CD4" s="1" t="n">
         <v>12.33</v>
       </c>
-      <c r="CD4" s="1" t="n">
+      <c r="CE4" s="1" t="n">
         <v>48.62</v>
       </c>
-      <c r="CE4" s="1" t="n">
+      <c r="CF4" s="1" t="n">
         <v>1439103046</v>
       </c>
-      <c r="CF4" s="1" t="n">
+      <c r="CG4" s="1" t="n">
         <v>14.04</v>
       </c>
-      <c r="CG4" s="1" t="n">
+      <c r="CH4" s="1" t="n">
         <v>92.26</v>
       </c>
-      <c r="CH4" s="1" t="n">
+      <c r="CI4" s="1" t="n">
         <v>513954758</v>
       </c>
-      <c r="CI4" s="1" t="n">
+      <c r="CJ4" s="1" t="n">
         <v>5.01</v>
       </c>
-      <c r="CJ4" s="1" t="n">
+      <c r="CK4" s="1" t="n">
         <v>71.83</v>
       </c>
-      <c r="CK4" s="1" t="n">
+      <c r="CL4" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="CL4" s="1" t="n">
+      <c r="CM4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="CM4" s="1" t="n">
+      <c r="CN4" s="1" t="n">
         <v>45</v>
-      </c>
-      <c r="CN4" s="1" t="n">
-        <v>0</v>
       </c>
       <c r="CO4" s="1" t="n">
         <v>0</v>
@@ -1226,24 +1240,27 @@
         <v>0</v>
       </c>
       <c r="CQ4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR4" s="1" t="n">
         <v>40.06</v>
       </c>
-      <c r="CR4" s="1" t="n">
+      <c r="CS4" s="1" t="n">
         <v>21.63</v>
       </c>
-      <c r="CS4" s="1"/>
       <c r="CT4" s="1"/>
       <c r="CU4" s="1"/>
       <c r="CV4" s="1"/>
       <c r="CW4" s="1"/>
       <c r="CX4" s="1"/>
+      <c r="CY4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>4751195380</v>
@@ -1258,247 +1275,247 @@
         <v>735.075</v>
       </c>
       <c r="G5" s="1" t="n">
+        <v>302115825</v>
+      </c>
+      <c r="H5" s="1" t="n">
         <v>37452.268</v>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="I5" s="1" t="n">
         <v>195176349</v>
       </c>
-      <c r="I5" s="1" t="n">
+      <c r="J5" s="1" t="n">
         <v>195176351</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="K5" s="1" t="n">
         <v>4.11</v>
       </c>
-      <c r="K5" s="1" t="n">
+      <c r="L5" s="1" t="n">
         <v>2992788185</v>
       </c>
-      <c r="L5" s="1" t="n">
+      <c r="M5" s="1" t="n">
         <v>62.99</v>
       </c>
-      <c r="M5" s="1" t="n">
+      <c r="N5" s="1" t="n">
         <v>195176349</v>
       </c>
-      <c r="N5" s="1" t="n">
+      <c r="O5" s="1" t="n">
         <v>4.11</v>
       </c>
-      <c r="O5" s="1" t="n">
+      <c r="P5" s="1" t="n">
         <v>1368054495</v>
       </c>
-      <c r="P5" s="1" t="n">
+      <c r="Q5" s="1" t="n">
         <v>28.79</v>
       </c>
-      <c r="R5" s="1" t="n">
+      <c r="S5" s="1" t="n">
         <v>195176349</v>
       </c>
-      <c r="S5" s="1" t="n">
+      <c r="T5" s="1" t="n">
         <v>3383140885</v>
       </c>
-      <c r="T5" s="1" t="n">
+      <c r="U5" s="1" t="n">
         <v>71.21</v>
       </c>
-      <c r="U5" s="1" t="n">
+      <c r="V5" s="1" t="n">
         <v>195176349</v>
       </c>
-      <c r="V5" s="1" t="n">
+      <c r="W5" s="1" t="n">
         <v>4.11</v>
       </c>
-      <c r="W5" s="1" t="n">
+      <c r="X5" s="1" t="n">
         <v>1172878146</v>
       </c>
-      <c r="X5" s="1" t="n">
+      <c r="Y5" s="1" t="n">
         <v>24.69</v>
       </c>
-      <c r="Z5" s="1" t="n">
+      <c r="AA5" s="1" t="n">
         <v>195176349</v>
       </c>
-      <c r="AA5" s="1" t="n">
+      <c r="AB5" s="1" t="n">
         <v>3578317234</v>
       </c>
-      <c r="AB5" s="1" t="n">
+      <c r="AC5" s="1" t="n">
         <v>75.31</v>
       </c>
-      <c r="AC5" s="1" t="n">
+      <c r="AD5" s="1" t="n">
         <v>195176349</v>
       </c>
-      <c r="AD5" s="1" t="n">
+      <c r="AE5" s="1" t="n">
         <v>4.11</v>
       </c>
-      <c r="AE5" s="1" t="n">
+      <c r="AF5" s="1" t="n">
         <v>977701797</v>
       </c>
-      <c r="AF5" s="1" t="n">
+      <c r="AG5" s="1" t="n">
         <v>20.58</v>
       </c>
-      <c r="AH5" s="1" t="n">
+      <c r="AI5" s="1" t="n">
         <v>15597770</v>
       </c>
-      <c r="AI5" s="1" t="n">
+      <c r="AJ5" s="1" t="n">
         <v>7154738</v>
       </c>
-      <c r="AJ5" s="1" t="n">
+      <c r="AK5" s="1" t="n">
         <v>3773493583</v>
       </c>
-      <c r="AK5" s="1" t="n">
+      <c r="AL5" s="1" t="n">
         <v>79.42</v>
       </c>
-      <c r="AL5" s="1" t="n">
+      <c r="AM5" s="1" t="n">
         <v>614939759</v>
       </c>
-      <c r="AM5" s="1" t="n">
+      <c r="AN5" s="1" t="n">
         <v>12.94</v>
       </c>
-      <c r="AN5" s="1" t="n">
+      <c r="AO5" s="1" t="n">
         <v>15597770</v>
       </c>
-      <c r="AO5" s="1" t="n">
+      <c r="AP5" s="1" t="n">
         <v>0.33</v>
       </c>
-      <c r="AP5" s="1" t="n">
+      <c r="AQ5" s="1" t="n">
         <v>144833181</v>
       </c>
-      <c r="AQ5" s="1" t="n">
+      <c r="AR5" s="1" t="n">
         <v>3.05</v>
       </c>
-      <c r="AR5" s="1" t="n">
+      <c r="AS5" s="1" t="n">
         <v>7154738</v>
       </c>
-      <c r="AS5" s="1" t="n">
+      <c r="AT5" s="1" t="n">
         <v>0.15</v>
       </c>
-      <c r="AT5" s="1" t="n">
+      <c r="AU5" s="1" t="n">
         <v>195176349</v>
       </c>
-      <c r="AU5" s="1" t="n">
+      <c r="AV5" s="1" t="n">
         <v>4.11</v>
       </c>
-      <c r="AW5" s="1" t="n">
+      <c r="AX5" s="1" t="n">
         <v>195176349</v>
       </c>
-      <c r="AX5" s="1" t="n">
+      <c r="AY5" s="1" t="n">
         <v>4556019031</v>
       </c>
-      <c r="AY5" s="1" t="n">
+      <c r="AZ5" s="1" t="n">
         <v>95.89</v>
       </c>
-      <c r="AZ5" s="1" t="n">
+      <c r="BA5" s="1" t="n">
         <v>195176349</v>
       </c>
-      <c r="BA5" s="1" t="n">
+      <c r="BB5" s="1" t="n">
         <v>4.11</v>
       </c>
-      <c r="BC5" s="1" t="n">
+      <c r="BD5" s="1" t="n">
         <v>1577508</v>
       </c>
-      <c r="BD5" s="1" t="n">
+      <c r="BE5" s="1" t="n">
         <v>1928718</v>
       </c>
-      <c r="BE5" s="1" t="n">
+      <c r="BF5" s="1" t="n">
         <v>2032838</v>
       </c>
-      <c r="BF5" s="1" t="n">
+      <c r="BG5" s="1" t="n">
         <v>88300180</v>
       </c>
-      <c r="BG5" s="1" t="n">
+      <c r="BH5" s="1" t="n">
         <v>52598628</v>
       </c>
-      <c r="BH5" s="1" t="n">
+      <c r="BI5" s="1" t="n">
         <v>25985967</v>
       </c>
-      <c r="BI5" s="1" t="n">
+      <c r="BJ5" s="1" t="n">
         <v>15597770</v>
       </c>
-      <c r="BJ5" s="1" t="n">
+      <c r="BK5" s="1" t="n">
         <v>7154738</v>
       </c>
-      <c r="BK5" s="1" t="n">
+      <c r="BL5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="BL5" s="1" t="n">
+      <c r="BM5" s="1" t="n">
         <v>4751195379</v>
       </c>
-      <c r="BM5" s="1" t="n">
+      <c r="BN5" s="1" t="n">
         <v>99070774</v>
       </c>
-      <c r="BN5" s="1" t="n">
+      <c r="BO5" s="1" t="n">
         <v>2.09</v>
       </c>
-      <c r="BO5" s="1" t="n">
+      <c r="BP5" s="1" t="n">
         <v>62.8</v>
       </c>
-      <c r="BP5" s="1" t="n">
+      <c r="BQ5" s="1" t="n">
         <v>100609959</v>
       </c>
-      <c r="BQ5" s="1" t="n">
+      <c r="BR5" s="1" t="n">
         <v>2.12</v>
       </c>
-      <c r="BR5" s="1" t="n">
+      <c r="BS5" s="1" t="n">
         <v>52.16</v>
       </c>
-      <c r="BS5" s="1" t="n">
+      <c r="BT5" s="1" t="n">
         <v>87228483</v>
       </c>
-      <c r="BT5" s="1" t="n">
+      <c r="BU5" s="1" t="n">
         <v>1.84</v>
       </c>
-      <c r="BU5" s="1" t="n">
+      <c r="BV5" s="1" t="n">
         <v>42.91</v>
       </c>
-      <c r="BV5" s="1" t="n">
+      <c r="BW5" s="1" t="n">
         <v>1505557846</v>
       </c>
-      <c r="BW5" s="1" t="n">
+      <c r="BX5" s="1" t="n">
         <v>31.69</v>
       </c>
-      <c r="BX5" s="1" t="n">
+      <c r="BY5" s="1" t="n">
         <v>17.05</v>
       </c>
-      <c r="BY5" s="1" t="n">
+      <c r="BZ5" s="1" t="n">
         <v>674349616</v>
       </c>
-      <c r="BZ5" s="1" t="n">
+      <c r="CA5" s="1" t="n">
         <v>14.19</v>
       </c>
-      <c r="CA5" s="1" t="n">
+      <c r="CB5" s="1" t="n">
         <v>12.82</v>
       </c>
-      <c r="CB5" s="1" t="n">
+      <c r="CC5" s="1" t="n">
         <v>667309208</v>
       </c>
-      <c r="CC5" s="1" t="n">
+      <c r="CD5" s="1" t="n">
         <v>14.05</v>
       </c>
-      <c r="CD5" s="1" t="n">
+      <c r="CE5" s="1" t="n">
         <v>25.68</v>
       </c>
-      <c r="CE5" s="1" t="n">
+      <c r="CF5" s="1" t="n">
         <v>1200448322</v>
       </c>
-      <c r="CF5" s="1" t="n">
+      <c r="CG5" s="1" t="n">
         <v>25.27</v>
       </c>
-      <c r="CG5" s="1" t="n">
+      <c r="CH5" s="1" t="n">
         <v>76.96</v>
       </c>
-      <c r="CH5" s="1" t="n">
+      <c r="CI5" s="1" t="n">
         <v>416621071</v>
       </c>
-      <c r="CI5" s="1" t="n">
+      <c r="CJ5" s="1" t="n">
         <v>8.77</v>
       </c>
-      <c r="CJ5" s="1" t="n">
+      <c r="CK5" s="1" t="n">
         <v>58.23</v>
       </c>
-      <c r="CK5" s="1" t="n">
+      <c r="CL5" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="CL5" s="1" t="n">
+      <c r="CM5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="CM5" s="1" t="n">
+      <c r="CN5" s="1" t="n">
         <v>50</v>
-      </c>
-      <c r="CN5" s="1" t="n">
-        <v>0</v>
       </c>
       <c r="CO5" s="1" t="n">
         <v>0</v>
@@ -1507,18 +1524,21 @@
         <v>0</v>
       </c>
       <c r="CQ5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR5" s="1" t="n">
         <v>39.42</v>
       </c>
-      <c r="CR5" s="1" t="n">
+      <c r="CS5" s="1" t="n">
         <v>20.24</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>4801353802</v>
@@ -1533,247 +1553,247 @@
         <v>745.955</v>
       </c>
       <c r="G6" s="1" t="n">
+        <v>30360368.5</v>
+      </c>
+      <c r="H6" s="1" t="n">
         <v>37510.256</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="I6" s="1" t="n">
         <v>195176515</v>
       </c>
-      <c r="I6" s="1" t="n">
+      <c r="J6" s="1" t="n">
         <v>195176517</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="K6" s="1" t="n">
         <v>4.07</v>
       </c>
-      <c r="K6" s="1" t="n">
+      <c r="L6" s="1" t="n">
         <v>3039512352</v>
       </c>
-      <c r="L6" s="1" t="n">
+      <c r="M6" s="1" t="n">
         <v>63.31</v>
       </c>
-      <c r="M6" s="1" t="n">
+      <c r="N6" s="1" t="n">
         <v>195176515</v>
       </c>
-      <c r="N6" s="1" t="n">
+      <c r="O6" s="1" t="n">
         <v>4.07</v>
       </c>
-      <c r="O6" s="1" t="n">
+      <c r="P6" s="1" t="n">
         <v>1371488418</v>
       </c>
-      <c r="P6" s="1" t="n">
+      <c r="Q6" s="1" t="n">
         <v>28.56</v>
       </c>
-      <c r="R6" s="1" t="n">
+      <c r="S6" s="1" t="n">
         <v>195176515</v>
       </c>
-      <c r="S6" s="1" t="n">
+      <c r="T6" s="1" t="n">
         <v>3429865384</v>
       </c>
-      <c r="T6" s="1" t="n">
+      <c r="U6" s="1" t="n">
         <v>71.44</v>
       </c>
-      <c r="U6" s="1" t="n">
+      <c r="V6" s="1" t="n">
         <v>195176515</v>
       </c>
-      <c r="V6" s="1" t="n">
+      <c r="W6" s="1" t="n">
         <v>4.07</v>
       </c>
-      <c r="W6" s="1" t="n">
+      <c r="X6" s="1" t="n">
         <v>1176311903</v>
       </c>
-      <c r="X6" s="1" t="n">
+      <c r="Y6" s="1" t="n">
         <v>24.5</v>
       </c>
-      <c r="Z6" s="1" t="n">
+      <c r="AA6" s="1" t="n">
         <v>195176515</v>
       </c>
-      <c r="AA6" s="1" t="n">
+      <c r="AB6" s="1" t="n">
         <v>3625041899</v>
       </c>
-      <c r="AB6" s="1" t="n">
+      <c r="AC6" s="1" t="n">
         <v>75.5</v>
       </c>
-      <c r="AC6" s="1" t="n">
+      <c r="AD6" s="1" t="n">
         <v>195176515</v>
       </c>
-      <c r="AD6" s="1" t="n">
+      <c r="AE6" s="1" t="n">
         <v>4.07</v>
       </c>
-      <c r="AE6" s="1" t="n">
+      <c r="AF6" s="1" t="n">
         <v>981135388</v>
       </c>
-      <c r="AF6" s="1" t="n">
+      <c r="AG6" s="1" t="n">
         <v>20.43</v>
       </c>
-      <c r="AH6" s="1" t="n">
+      <c r="AI6" s="1" t="n">
         <v>15597735</v>
       </c>
-      <c r="AI6" s="1" t="n">
+      <c r="AJ6" s="1" t="n">
         <v>7154732</v>
       </c>
-      <c r="AJ6" s="1" t="n">
+      <c r="AK6" s="1" t="n">
         <v>3820218414</v>
       </c>
-      <c r="AK6" s="1" t="n">
+      <c r="AL6" s="1" t="n">
         <v>79.57</v>
       </c>
-      <c r="AL6" s="1" t="n">
+      <c r="AM6" s="1" t="n">
         <v>617743135</v>
       </c>
-      <c r="AM6" s="1" t="n">
+      <c r="AN6" s="1" t="n">
         <v>12.87</v>
       </c>
-      <c r="AN6" s="1" t="n">
+      <c r="AO6" s="1" t="n">
         <v>15597735</v>
       </c>
-      <c r="AO6" s="1" t="n">
+      <c r="AP6" s="1" t="n">
         <v>0.32</v>
       </c>
-      <c r="AP6" s="1" t="n">
+      <c r="AQ6" s="1" t="n">
         <v>145463271</v>
       </c>
-      <c r="AQ6" s="1" t="n">
+      <c r="AR6" s="1" t="n">
         <v>3.03</v>
       </c>
-      <c r="AR6" s="1" t="n">
+      <c r="AS6" s="1" t="n">
         <v>7154732</v>
       </c>
-      <c r="AS6" s="1" t="n">
+      <c r="AT6" s="1" t="n">
         <v>0.15</v>
       </c>
-      <c r="AT6" s="1" t="n">
+      <c r="AU6" s="1" t="n">
         <v>195176515</v>
       </c>
-      <c r="AU6" s="1" t="n">
+      <c r="AV6" s="1" t="n">
         <v>4.07</v>
       </c>
-      <c r="AW6" s="1" t="n">
+      <c r="AX6" s="1" t="n">
         <v>195176515</v>
       </c>
-      <c r="AX6" s="1" t="n">
+      <c r="AY6" s="1" t="n">
         <v>4606177287</v>
       </c>
-      <c r="AY6" s="1" t="n">
+      <c r="AZ6" s="1" t="n">
         <v>95.93</v>
       </c>
-      <c r="AZ6" s="1" t="n">
+      <c r="BA6" s="1" t="n">
         <v>195176515</v>
       </c>
-      <c r="BA6" s="1" t="n">
+      <c r="BB6" s="1" t="n">
         <v>4.07</v>
       </c>
-      <c r="BC6" s="1" t="n">
+      <c r="BD6" s="1" t="n">
         <v>1577504</v>
       </c>
-      <c r="BD6" s="1" t="n">
+      <c r="BE6" s="1" t="n">
         <v>1928713</v>
       </c>
-      <c r="BE6" s="1" t="n">
+      <c r="BF6" s="1" t="n">
         <v>2032834</v>
       </c>
-      <c r="BF6" s="1" t="n">
+      <c r="BG6" s="1" t="n">
         <v>88300278</v>
       </c>
-      <c r="BG6" s="1" t="n">
+      <c r="BH6" s="1" t="n">
         <v>52598704</v>
       </c>
-      <c r="BH6" s="1" t="n">
+      <c r="BI6" s="1" t="n">
         <v>25986013</v>
       </c>
-      <c r="BI6" s="1" t="n">
+      <c r="BJ6" s="1" t="n">
         <v>15597735</v>
       </c>
-      <c r="BJ6" s="1" t="n">
+      <c r="BK6" s="1" t="n">
         <v>7154732</v>
       </c>
-      <c r="BK6" s="1" t="n">
+      <c r="BL6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="BL6" s="1" t="n">
+      <c r="BM6" s="1" t="n">
         <v>4801353801</v>
       </c>
-      <c r="BM6" s="1" t="n">
+      <c r="BN6" s="1" t="n">
         <v>99945922</v>
       </c>
-      <c r="BN6" s="1" t="n">
+      <c r="BO6" s="1" t="n">
         <v>2.08</v>
       </c>
-      <c r="BO6" s="1" t="n">
+      <c r="BP6" s="1" t="n">
         <v>63.36</v>
       </c>
-      <c r="BP6" s="1" t="n">
+      <c r="BQ6" s="1" t="n">
         <v>102799352</v>
       </c>
-      <c r="BQ6" s="1" t="n">
+      <c r="BR6" s="1" t="n">
         <v>2.14</v>
       </c>
-      <c r="BR6" s="1" t="n">
+      <c r="BS6" s="1" t="n">
         <v>53.3</v>
       </c>
-      <c r="BS6" s="1" t="n">
+      <c r="BT6" s="1" t="n">
         <v>87572045</v>
       </c>
-      <c r="BT6" s="1" t="n">
+      <c r="BU6" s="1" t="n">
         <v>1.82</v>
       </c>
-      <c r="BU6" s="1" t="n">
+      <c r="BV6" s="1" t="n">
         <v>43.08</v>
       </c>
-      <c r="BV6" s="1" t="n">
+      <c r="BW6" s="1" t="n">
         <v>1520907972</v>
       </c>
-      <c r="BW6" s="1" t="n">
+      <c r="BX6" s="1" t="n">
         <v>31.68</v>
       </c>
-      <c r="BX6" s="1" t="n">
+      <c r="BY6" s="1" t="n">
         <v>17.22</v>
       </c>
-      <c r="BY6" s="1" t="n">
+      <c r="BZ6" s="1" t="n">
         <v>680229117</v>
       </c>
-      <c r="BZ6" s="1" t="n">
+      <c r="CA6" s="1" t="n">
         <v>14.17</v>
       </c>
-      <c r="CA6" s="1" t="n">
+      <c r="CB6" s="1" t="n">
         <v>12.93</v>
       </c>
-      <c r="CB6" s="1" t="n">
+      <c r="CC6" s="1" t="n">
         <v>677875599</v>
       </c>
-      <c r="CC6" s="1" t="n">
+      <c r="CD6" s="1" t="n">
         <v>14.12</v>
       </c>
-      <c r="CD6" s="1" t="n">
+      <c r="CE6" s="1" t="n">
         <v>26.09</v>
       </c>
-      <c r="CE6" s="1" t="n">
+      <c r="CF6" s="1" t="n">
         <v>1210936285</v>
       </c>
-      <c r="CF6" s="1" t="n">
+      <c r="CG6" s="1" t="n">
         <v>25.22</v>
       </c>
-      <c r="CG6" s="1" t="n">
+      <c r="CH6" s="1" t="n">
         <v>77.64</v>
       </c>
-      <c r="CH6" s="1" t="n">
+      <c r="CI6" s="1" t="n">
         <v>421087318</v>
       </c>
-      <c r="CI6" s="1" t="n">
+      <c r="CJ6" s="1" t="n">
         <v>8.77</v>
       </c>
-      <c r="CJ6" s="1" t="n">
+      <c r="CK6" s="1" t="n">
         <v>58.85</v>
       </c>
-      <c r="CK6" s="1" t="n">
+      <c r="CL6" s="1" t="n">
         <v>191</v>
       </c>
-      <c r="CL6" s="1" t="n">
+      <c r="CM6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="CM6" s="1" t="n">
+      <c r="CN6" s="1" t="n">
         <v>95.5</v>
-      </c>
-      <c r="CN6" s="1" t="n">
-        <v>0</v>
       </c>
       <c r="CO6" s="1" t="n">
         <v>0</v>
@@ -1782,36 +1802,39 @@
         <v>0</v>
       </c>
       <c r="CQ6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR6" s="1" t="n">
         <v>39.6</v>
       </c>
-      <c r="CR6" s="1" t="n">
+      <c r="CS6" s="1" t="n">
         <v>20.33</v>
       </c>
-      <c r="CS6" s="8" t="n">
+      <c r="CT6" s="8" t="n">
         <v>141963461</v>
       </c>
-      <c r="CT6" s="8" t="n">
+      <c r="CU6" s="8" t="n">
         <v>53213054</v>
       </c>
-      <c r="CU6" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="CV6" s="8" t="n">
+      <c r="CV6" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="CW6" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="CW6" s="8" t="n">
+      <c r="CX6" s="8" t="n">
         <v>49.78</v>
       </c>
-      <c r="CX6" s="8" t="n">
+      <c r="CY6" s="8" t="n">
         <v>16.57</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="220.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>5703538013</v>
@@ -1826,262 +1849,262 @@
         <v>743.124</v>
       </c>
       <c r="G7" s="1" t="n">
+        <v>25414840.8</v>
+      </c>
+      <c r="H7" s="1" t="n">
         <v>19420.394</v>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="I7" s="1" t="n">
         <v>195177143</v>
       </c>
-      <c r="I7" s="1" t="n">
+      <c r="J7" s="1" t="n">
         <v>195177145</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="K7" s="1" t="n">
         <v>3.42</v>
       </c>
-      <c r="K7" s="1" t="n">
+      <c r="L7" s="1" t="n">
         <v>3956716879</v>
       </c>
-      <c r="L7" s="1" t="n">
+      <c r="M7" s="1" t="n">
         <v>69.37</v>
       </c>
-      <c r="M7" s="1" t="n">
+      <c r="N7" s="1" t="n">
         <v>195177143</v>
       </c>
-      <c r="N7" s="1" t="n">
+      <c r="O7" s="1" t="n">
         <v>3.42</v>
       </c>
-      <c r="O7" s="1" t="n">
+      <c r="P7" s="1" t="n">
         <v>1356466846</v>
       </c>
-      <c r="P7" s="1" t="n">
+      <c r="Q7" s="1" t="n">
         <v>23.78</v>
       </c>
-      <c r="Q7" s="1" t="n">
+      <c r="R7" s="1" t="n">
         <v>5703538013</v>
       </c>
-      <c r="R7" s="1" t="n">
+      <c r="S7" s="1" t="n">
         <v>195177143</v>
       </c>
-      <c r="S7" s="1" t="n">
+      <c r="T7" s="1" t="n">
         <v>4347071167</v>
       </c>
-      <c r="T7" s="1" t="n">
+      <c r="U7" s="1" t="n">
         <v>76.22</v>
       </c>
-      <c r="U7" s="1" t="n">
+      <c r="V7" s="1" t="n">
         <v>195177143</v>
       </c>
-      <c r="V7" s="1" t="n">
+      <c r="W7" s="1" t="n">
         <v>3.42</v>
       </c>
-      <c r="W7" s="1" t="n">
+      <c r="X7" s="1" t="n">
         <v>1161289703</v>
       </c>
-      <c r="X7" s="1" t="n">
+      <c r="Y7" s="1" t="n">
         <v>20.36</v>
       </c>
-      <c r="Y7" s="1" t="n">
+      <c r="Z7" s="1" t="n">
         <v>5703538013</v>
       </c>
-      <c r="Z7" s="1" t="n">
+      <c r="AA7" s="1" t="n">
         <v>195177143</v>
       </c>
-      <c r="AA7" s="1" t="n">
+      <c r="AB7" s="1" t="n">
         <v>4542248310</v>
       </c>
-      <c r="AB7" s="1" t="n">
+      <c r="AC7" s="1" t="n">
         <v>79.64</v>
       </c>
-      <c r="AC7" s="1" t="n">
+      <c r="AD7" s="1" t="n">
         <v>195177143</v>
       </c>
-      <c r="AD7" s="1" t="n">
+      <c r="AE7" s="1" t="n">
         <v>3.42</v>
       </c>
-      <c r="AE7" s="1" t="n">
+      <c r="AF7" s="1" t="n">
         <v>966112560</v>
       </c>
-      <c r="AF7" s="1" t="n">
+      <c r="AG7" s="1" t="n">
         <v>16.94</v>
       </c>
-      <c r="AG7" s="1" t="n">
+      <c r="AH7" s="1" t="n">
         <v>5703538013</v>
       </c>
-      <c r="AH7" s="1" t="n">
+      <c r="AI7" s="1" t="n">
         <v>15597783</v>
       </c>
-      <c r="AI7" s="1" t="n">
+      <c r="AJ7" s="1" t="n">
         <v>7154776</v>
       </c>
-      <c r="AJ7" s="1" t="n">
+      <c r="AK7" s="1" t="n">
         <v>4737425453</v>
       </c>
-      <c r="AK7" s="1" t="n">
+      <c r="AL7" s="1" t="n">
         <v>83.06</v>
       </c>
-      <c r="AL7" s="1" t="n">
+      <c r="AM7" s="1" t="n">
         <v>605921078</v>
       </c>
-      <c r="AM7" s="1" t="n">
+      <c r="AN7" s="1" t="n">
         <v>10.62</v>
       </c>
-      <c r="AN7" s="1" t="n">
+      <c r="AO7" s="1" t="n">
         <v>15597783</v>
       </c>
-      <c r="AO7" s="1" t="n">
+      <c r="AP7" s="1" t="n">
         <v>0.27</v>
       </c>
-      <c r="AP7" s="1" t="n">
+      <c r="AQ7" s="1" t="n">
         <v>142261780</v>
       </c>
-      <c r="AQ7" s="1" t="n">
+      <c r="AR7" s="1" t="n">
         <v>2.49</v>
       </c>
-      <c r="AR7" s="1" t="n">
+      <c r="AS7" s="1" t="n">
         <v>7154776</v>
       </c>
-      <c r="AS7" s="1" t="n">
+      <c r="AT7" s="1" t="n">
         <v>0.13</v>
       </c>
-      <c r="AT7" s="1" t="n">
+      <c r="AU7" s="1" t="n">
         <v>195177143</v>
       </c>
-      <c r="AU7" s="1" t="n">
+      <c r="AV7" s="1" t="n">
         <v>3.42</v>
       </c>
-      <c r="AV7" s="1" t="n">
+      <c r="AW7" s="1" t="n">
         <v>5703538013</v>
       </c>
-      <c r="AW7" s="1" t="n">
+      <c r="AX7" s="1" t="n">
         <v>195177143</v>
       </c>
-      <c r="AX7" s="1" t="n">
+      <c r="AY7" s="1" t="n">
         <v>5508360870</v>
       </c>
-      <c r="AY7" s="1" t="n">
+      <c r="AZ7" s="1" t="n">
         <v>96.58</v>
       </c>
-      <c r="AZ7" s="1" t="n">
+      <c r="BA7" s="1" t="n">
         <v>195177143</v>
       </c>
-      <c r="BA7" s="1" t="n">
+      <c r="BB7" s="1" t="n">
         <v>3.42</v>
       </c>
-      <c r="BB7" s="1" t="n">
+      <c r="BC7" s="1" t="n">
         <v>5703538013</v>
       </c>
-      <c r="BC7" s="1" t="n">
+      <c r="BD7" s="1" t="n">
         <v>1577512</v>
       </c>
-      <c r="BD7" s="1" t="n">
+      <c r="BE7" s="1" t="n">
         <v>1928707</v>
       </c>
-      <c r="BE7" s="1" t="n">
+      <c r="BF7" s="1" t="n">
         <v>2032827</v>
       </c>
-      <c r="BF7" s="1" t="n">
+      <c r="BG7" s="1" t="n">
         <v>88300441</v>
       </c>
-      <c r="BG7" s="1" t="n">
+      <c r="BH7" s="1" t="n">
         <v>52598348</v>
       </c>
-      <c r="BH7" s="1" t="n">
+      <c r="BI7" s="1" t="n">
         <v>25986747</v>
       </c>
-      <c r="BI7" s="1" t="n">
+      <c r="BJ7" s="1" t="n">
         <v>15597783</v>
       </c>
-      <c r="BJ7" s="1" t="n">
+      <c r="BK7" s="1" t="n">
         <v>7154776</v>
       </c>
-      <c r="BK7" s="1" t="n">
+      <c r="BL7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="BL7" s="1" t="n">
+      <c r="BM7" s="1" t="n">
         <v>5703538012</v>
       </c>
-      <c r="BM7" s="1" t="n">
+      <c r="BN7" s="1" t="n">
         <v>158430210</v>
       </c>
-      <c r="BN7" s="1" t="n">
+      <c r="BO7" s="1" t="n">
         <v>2.78</v>
       </c>
-      <c r="BO7" s="1" t="n">
+      <c r="BP7" s="1" t="n">
         <v>100.43</v>
       </c>
-      <c r="BP7" s="1" t="n">
+      <c r="BQ7" s="1" t="n">
         <v>47141238</v>
       </c>
-      <c r="BQ7" s="1" t="n">
+      <c r="BR7" s="1" t="n">
         <v>0.83</v>
       </c>
-      <c r="BR7" s="1" t="n">
+      <c r="BS7" s="1" t="n">
         <v>24.44</v>
       </c>
-      <c r="BS7" s="1" t="n">
+      <c r="BT7" s="1" t="n">
         <v>101577369</v>
       </c>
-      <c r="BT7" s="1" t="n">
+      <c r="BU7" s="1" t="n">
         <v>1.78</v>
       </c>
-      <c r="BU7" s="1" t="n">
+      <c r="BV7" s="1" t="n">
         <v>49.97</v>
       </c>
-      <c r="BV7" s="1" t="n">
+      <c r="BW7" s="1" t="n">
         <v>1801292574</v>
       </c>
-      <c r="BW7" s="1" t="n">
+      <c r="BX7" s="1" t="n">
         <v>31.58</v>
       </c>
-      <c r="BX7" s="1" t="n">
+      <c r="BY7" s="1" t="n">
         <v>20.4</v>
       </c>
-      <c r="BY7" s="1" t="n">
+      <c r="BZ7" s="1" t="n">
         <v>1059005580</v>
       </c>
-      <c r="BZ7" s="1" t="n">
+      <c r="CA7" s="1" t="n">
         <v>18.57</v>
       </c>
-      <c r="CA7" s="1" t="n">
+      <c r="CB7" s="1" t="n">
         <v>20.13</v>
       </c>
-      <c r="CB7" s="1" t="n">
+      <c r="CC7" s="1" t="n">
         <v>496502323</v>
       </c>
-      <c r="CC7" s="1" t="n">
+      <c r="CD7" s="1" t="n">
         <v>8.71</v>
       </c>
-      <c r="CD7" s="1" t="n">
+      <c r="CE7" s="1" t="n">
         <v>19.11</v>
       </c>
-      <c r="CE7" s="1" t="n">
+      <c r="CF7" s="1" t="n">
         <v>1678462352</v>
       </c>
-      <c r="CF7" s="1" t="n">
+      <c r="CG7" s="1" t="n">
         <v>29.43</v>
       </c>
-      <c r="CG7" s="1" t="n">
+      <c r="CH7" s="1" t="n">
         <v>107.61</v>
       </c>
-      <c r="CH7" s="1" t="n">
+      <c r="CI7" s="1" t="n">
         <v>361126352</v>
       </c>
-      <c r="CI7" s="1" t="n">
+      <c r="CJ7" s="1" t="n">
         <v>6.33</v>
       </c>
-      <c r="CJ7" s="1" t="n">
+      <c r="CK7" s="1" t="n">
         <v>50.47</v>
       </c>
-      <c r="CK7" s="1" t="n">
+      <c r="CL7" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="CL7" s="1" t="n">
+      <c r="CM7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="CM7" s="1" t="n">
+      <c r="CN7" s="1" t="n">
         <v>7</v>
-      </c>
-      <c r="CN7" s="1" t="n">
-        <v>0</v>
       </c>
       <c r="CO7" s="1" t="n">
         <v>0</v>
@@ -2090,343 +2113,660 @@
         <v>0</v>
       </c>
       <c r="CQ7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR7" s="1" t="n">
         <v>38.85</v>
       </c>
-      <c r="CR7" s="1" t="n">
+      <c r="CS7" s="1" t="n">
         <v>19.88</v>
       </c>
-      <c r="CS7" s="1" t="n">
+      <c r="CT7" s="1" t="n">
         <v>176740874</v>
       </c>
-      <c r="CT7" s="1" t="n">
+      <c r="CU7" s="1" t="n">
         <v>18436269</v>
       </c>
-      <c r="CU7" s="1" t="n">
+      <c r="CV7" s="1" t="n">
         <v>90.55</v>
       </c>
-      <c r="CV7" s="1" t="n">
+      <c r="CW7" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="CW7" s="1" t="n">
+      <c r="CX7" s="1" t="n">
         <v>193.44</v>
       </c>
-      <c r="CX7" s="1" t="n">
+      <c r="CY7" s="1" t="n">
         <v>21.27</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>76</v>
+    <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" s="0" t="n">
+        <v>78</v>
+      </c>
+      <c r="C8" s="1" t="n">
         <v>4001021733</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>195152207</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>0.0488</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <v>743.056</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8" s="1" t="n">
+        <v>36261132.8</v>
+      </c>
+      <c r="H8" s="1" t="n">
         <v>19457.102</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="I8" s="1" t="n">
         <v>195152207</v>
       </c>
-      <c r="I8" s="0" t="n">
+      <c r="J8" s="1" t="n">
         <v>195152209</v>
       </c>
-      <c r="J8" s="0" t="n">
+      <c r="K8" s="1" t="n">
         <v>4.88</v>
       </c>
-      <c r="K8" s="0" t="n">
+      <c r="L8" s="1" t="n">
         <v>2102612798</v>
       </c>
-      <c r="L8" s="0" t="n">
+      <c r="M8" s="1" t="n">
         <v>52.55</v>
       </c>
-      <c r="M8" s="0" t="n">
+      <c r="N8" s="1" t="n">
         <v>195152207</v>
       </c>
-      <c r="N8" s="0" t="n">
+      <c r="O8" s="1" t="n">
         <v>4.88</v>
       </c>
-      <c r="O8" s="0" t="n">
+      <c r="P8" s="1" t="n">
         <v>1508104519</v>
       </c>
-      <c r="P8" s="0" t="n">
+      <c r="Q8" s="1" t="n">
         <v>37.69</v>
       </c>
-      <c r="Q8" s="0" t="n">
+      <c r="R8" s="1" t="n">
         <v>4001021733</v>
       </c>
-      <c r="R8" s="0" t="n">
+      <c r="S8" s="1" t="n">
         <v>195152207</v>
       </c>
-      <c r="S8" s="0" t="n">
+      <c r="T8" s="1" t="n">
         <v>2492917214</v>
       </c>
-      <c r="T8" s="0" t="n">
+      <c r="U8" s="1" t="n">
         <v>62.31</v>
       </c>
-      <c r="U8" s="0" t="n">
+      <c r="V8" s="1" t="n">
         <v>195152207</v>
       </c>
-      <c r="V8" s="0" t="n">
+      <c r="W8" s="1" t="n">
         <v>4.88</v>
       </c>
-      <c r="W8" s="0" t="n">
+      <c r="X8" s="1" t="n">
         <v>1312952312</v>
       </c>
-      <c r="X8" s="0" t="n">
+      <c r="Y8" s="1" t="n">
         <v>32.82</v>
       </c>
-      <c r="Y8" s="0" t="n">
+      <c r="Z8" s="1" t="n">
         <v>4001021733</v>
       </c>
-      <c r="Z8" s="0" t="n">
+      <c r="AA8" s="1" t="n">
         <v>195152207</v>
       </c>
-      <c r="AA8" s="0" t="n">
+      <c r="AB8" s="1" t="n">
         <v>2688069421</v>
       </c>
-      <c r="AB8" s="0" t="n">
+      <c r="AC8" s="1" t="n">
         <v>67.18</v>
       </c>
-      <c r="AC8" s="0" t="n">
+      <c r="AD8" s="1" t="n">
         <v>195152207</v>
       </c>
-      <c r="AD8" s="0" t="n">
+      <c r="AE8" s="1" t="n">
         <v>4.88</v>
       </c>
-      <c r="AE8" s="0" t="n">
+      <c r="AF8" s="1" t="n">
         <v>1117800105</v>
       </c>
-      <c r="AF8" s="0" t="n">
+      <c r="AG8" s="1" t="n">
         <v>27.94</v>
       </c>
-      <c r="AG8" s="0" t="n">
+      <c r="AH8" s="1" t="n">
         <v>4001021733</v>
       </c>
-      <c r="AH8" s="0" t="n">
+      <c r="AI8" s="1" t="n">
         <v>15597054</v>
       </c>
-      <c r="AI8" s="0" t="n">
+      <c r="AJ8" s="1" t="n">
         <v>7154003</v>
       </c>
-      <c r="AJ8" s="0" t="n">
+      <c r="AK8" s="1" t="n">
         <v>2883221628</v>
       </c>
-      <c r="AK8" s="0" t="n">
+      <c r="AL8" s="1" t="n">
         <v>72.06</v>
       </c>
-      <c r="AL8" s="0" t="n">
+      <c r="AM8" s="1" t="n">
         <v>716178357</v>
       </c>
-      <c r="AM8" s="0" t="n">
+      <c r="AN8" s="1" t="n">
         <v>17.9</v>
       </c>
-      <c r="AN8" s="0" t="n">
+      <c r="AO8" s="1" t="n">
         <v>15597054</v>
       </c>
-      <c r="AO8" s="0" t="n">
+      <c r="AP8" s="1" t="n">
         <v>0.39</v>
       </c>
-      <c r="AP8" s="0" t="n">
+      <c r="AQ8" s="1" t="n">
         <v>183718484</v>
       </c>
-      <c r="AQ8" s="0" t="n">
+      <c r="AR8" s="1" t="n">
         <v>4.59</v>
       </c>
-      <c r="AR8" s="0" t="n">
+      <c r="AS8" s="1" t="n">
         <v>7154003</v>
       </c>
-      <c r="AS8" s="0" t="n">
+      <c r="AT8" s="1" t="n">
         <v>0.18</v>
       </c>
-      <c r="AT8" s="0" t="n">
+      <c r="AU8" s="1" t="n">
         <v>195152207</v>
       </c>
-      <c r="AU8" s="0" t="n">
+      <c r="AV8" s="1" t="n">
         <v>4.88</v>
       </c>
-      <c r="AV8" s="0" t="n">
+      <c r="AW8" s="1" t="n">
         <v>4001021733</v>
       </c>
-      <c r="AW8" s="0" t="n">
+      <c r="AX8" s="1" t="n">
         <v>195152207</v>
       </c>
-      <c r="AX8" s="0" t="n">
+      <c r="AY8" s="1" t="n">
         <v>3805869526</v>
       </c>
-      <c r="AY8" s="0" t="n">
+      <c r="AZ8" s="1" t="n">
         <v>95.12</v>
       </c>
-      <c r="AZ8" s="0" t="n">
+      <c r="BA8" s="1" t="n">
         <v>195152207</v>
       </c>
-      <c r="BA8" s="0" t="n">
+      <c r="BB8" s="1" t="n">
         <v>4.88</v>
       </c>
-      <c r="BB8" s="0" t="n">
+      <c r="BC8" s="1" t="n">
         <v>4001021733</v>
       </c>
-      <c r="BC8" s="0" t="n">
+      <c r="BD8" s="1" t="n">
         <v>1577476</v>
       </c>
-      <c r="BD8" s="0" t="n">
+      <c r="BE8" s="1" t="n">
         <v>1928308</v>
       </c>
-      <c r="BE8" s="0" t="n">
+      <c r="BF8" s="1" t="n">
         <v>2032477</v>
       </c>
-      <c r="BF8" s="0" t="n">
+      <c r="BG8" s="1" t="n">
         <v>88289173</v>
       </c>
-      <c r="BG8" s="0" t="n">
+      <c r="BH8" s="1" t="n">
         <v>52590873</v>
       </c>
-      <c r="BH8" s="0" t="n">
+      <c r="BI8" s="1" t="n">
         <v>25982841</v>
       </c>
-      <c r="BI8" s="0" t="n">
+      <c r="BJ8" s="1" t="n">
         <v>15597054</v>
       </c>
-      <c r="BJ8" s="0" t="n">
+      <c r="BK8" s="1" t="n">
         <v>7154003</v>
       </c>
-      <c r="BK8" s="0" t="n">
+      <c r="BL8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="BL8" s="0" t="n">
+      <c r="BM8" s="1" t="n">
         <v>4001021732</v>
       </c>
-      <c r="BM8" s="0" t="n">
+      <c r="BN8" s="1" t="n">
         <v>84570913</v>
       </c>
-      <c r="BN8" s="0" t="n">
+      <c r="BO8" s="1" t="n">
         <v>2.11</v>
       </c>
-      <c r="BO8" s="0" t="n">
+      <c r="BP8" s="1" t="n">
         <v>53.61</v>
       </c>
-      <c r="BP8" s="0" t="n">
+      <c r="BQ8" s="1" t="n">
         <v>29287242</v>
       </c>
-      <c r="BQ8" s="0" t="n">
+      <c r="BR8" s="1" t="n">
         <v>0.73</v>
       </c>
-      <c r="BR8" s="0" t="n">
+      <c r="BS8" s="1" t="n">
         <v>15.19</v>
       </c>
-      <c r="BS8" s="0" t="n">
+      <c r="BT8" s="1" t="n">
         <v>61358756</v>
       </c>
-      <c r="BT8" s="0" t="n">
+      <c r="BU8" s="1" t="n">
         <v>1.53</v>
       </c>
-      <c r="BU8" s="0" t="n">
+      <c r="BV8" s="1" t="n">
         <v>30.19</v>
       </c>
-      <c r="BV8" s="0" t="n">
+      <c r="BW8" s="1" t="n">
         <v>1199564460</v>
       </c>
-      <c r="BW8" s="0" t="n">
+      <c r="BX8" s="1" t="n">
         <v>29.98</v>
       </c>
-      <c r="BX8" s="0" t="n">
+      <c r="BY8" s="1" t="n">
         <v>13.59</v>
       </c>
-      <c r="BY8" s="0" t="n">
+      <c r="BZ8" s="1" t="n">
         <v>687921261</v>
       </c>
-      <c r="BZ8" s="0" t="n">
+      <c r="CA8" s="1" t="n">
         <v>17.19</v>
       </c>
-      <c r="CA8" s="0" t="n">
+      <c r="CB8" s="1" t="n">
         <v>13.08</v>
       </c>
-      <c r="CB8" s="0" t="n">
+      <c r="CC8" s="1" t="n">
         <v>327920366</v>
       </c>
-      <c r="CC8" s="0" t="n">
+      <c r="CD8" s="1" t="n">
         <v>8.2</v>
       </c>
-      <c r="CD8" s="0" t="n">
+      <c r="CE8" s="1" t="n">
         <v>12.62</v>
       </c>
-      <c r="CE8" s="0" t="n">
+      <c r="CF8" s="1" t="n">
         <v>1289690846</v>
       </c>
-      <c r="CF8" s="0" t="n">
+      <c r="CG8" s="1" t="n">
         <v>32.23</v>
       </c>
-      <c r="CG8" s="0" t="n">
+      <c r="CH8" s="1" t="n">
         <v>82.69</v>
       </c>
-      <c r="CH8" s="0" t="n">
+      <c r="CI8" s="1" t="n">
         <v>320707874</v>
       </c>
-      <c r="CI8" s="0" t="n">
+      <c r="CJ8" s="1" t="n">
         <v>8.02</v>
       </c>
-      <c r="CJ8" s="0" t="n">
+      <c r="CK8" s="1" t="n">
         <v>44.83</v>
       </c>
-      <c r="CK8" s="0" t="n">
+      <c r="CL8" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="CL8" s="0" t="n">
+      <c r="CM8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="CM8" s="0" t="n">
+      <c r="CN8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="CN8" s="0" t="n">
+      <c r="CO8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="CO8" s="0" t="n">
+      <c r="CP8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="CP8" s="0" t="n">
+      <c r="CQ8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="CQ8" s="0" t="n">
+      <c r="CR8" s="1" t="n">
         <v>45.92</v>
       </c>
-      <c r="CR8" s="0" t="n">
+      <c r="CS8" s="1" t="n">
         <v>25.68</v>
       </c>
-      <c r="CS8" s="0" t="n">
+      <c r="CT8" s="1" t="n">
         <v>176719170</v>
       </c>
-      <c r="CT8" s="0" t="n">
+      <c r="CU8" s="1" t="n">
         <v>18433037</v>
       </c>
-      <c r="CU8" s="0" t="n">
+      <c r="CV8" s="1" t="n">
         <v>90.55</v>
       </c>
-      <c r="CV8" s="0" t="n">
+      <c r="CW8" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="CW8" s="0" t="n">
+      <c r="CX8" s="1" t="n">
         <v>92.89</v>
       </c>
-      <c r="CX8" s="0" t="n">
+      <c r="CY8" s="1" t="n">
         <v>11.77</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>3960985633</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>195175086</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>0.0493</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>736.66</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>36317338</v>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>19630.002</v>
+      </c>
+      <c r="I9" s="0" t="n">
+        <v>195175086</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>195175088</v>
+      </c>
+      <c r="K9" s="0" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="L9" s="0" t="n">
+        <v>2083432195</v>
+      </c>
+      <c r="M9" s="0" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="N9" s="0" t="n">
+        <v>195175086</v>
+      </c>
+      <c r="O9" s="0" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="P9" s="0" t="n">
+        <v>1487203264</v>
+      </c>
+      <c r="Q9" s="0" t="n">
+        <v>37.55</v>
+      </c>
+      <c r="R9" s="0" t="n">
+        <v>3960985633</v>
+      </c>
+      <c r="S9" s="0" t="n">
+        <v>195175086</v>
+      </c>
+      <c r="T9" s="0" t="n">
+        <v>2473782369</v>
+      </c>
+      <c r="U9" s="0" t="n">
+        <v>62.45</v>
+      </c>
+      <c r="V9" s="0" t="n">
+        <v>195175086</v>
+      </c>
+      <c r="W9" s="0" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="X9" s="0" t="n">
+        <v>1292028178</v>
+      </c>
+      <c r="Y9" s="0" t="n">
+        <v>32.62</v>
+      </c>
+      <c r="Z9" s="0" t="n">
+        <v>3960985633</v>
+      </c>
+      <c r="AA9" s="0" t="n">
+        <v>195175086</v>
+      </c>
+      <c r="AB9" s="0" t="n">
+        <v>2668957455</v>
+      </c>
+      <c r="AC9" s="0" t="n">
+        <v>67.38</v>
+      </c>
+      <c r="AD9" s="0" t="n">
+        <v>195175086</v>
+      </c>
+      <c r="AE9" s="0" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="AF9" s="0" t="n">
+        <v>1096853092</v>
+      </c>
+      <c r="AG9" s="0" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="AH9" s="0" t="n">
+        <v>3960985633</v>
+      </c>
+      <c r="AI9" s="0" t="n">
+        <v>15597804</v>
+      </c>
+      <c r="AJ9" s="0" t="n">
+        <v>7154801</v>
+      </c>
+      <c r="AK9" s="0" t="n">
+        <v>2864132541</v>
+      </c>
+      <c r="AL9" s="0" t="n">
+        <v>72.31</v>
+      </c>
+      <c r="AM9" s="0" t="n">
+        <v>695077524</v>
+      </c>
+      <c r="AN9" s="0" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="AO9" s="0" t="n">
+        <v>15597804</v>
+      </c>
+      <c r="AP9" s="0" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AQ9" s="0" t="n">
+        <v>183847877</v>
+      </c>
+      <c r="AR9" s="0" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AS9" s="0" t="n">
+        <v>7154801</v>
+      </c>
+      <c r="AT9" s="0" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AU9" s="0" t="n">
+        <v>195175086</v>
+      </c>
+      <c r="AV9" s="0" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="AW9" s="0" t="n">
+        <v>3960985633</v>
+      </c>
+      <c r="AX9" s="0" t="n">
+        <v>195175086</v>
+      </c>
+      <c r="AY9" s="0" t="n">
+        <v>3765810547</v>
+      </c>
+      <c r="AZ9" s="0" t="n">
+        <v>95.07</v>
+      </c>
+      <c r="BA9" s="0" t="n">
+        <v>195175086</v>
+      </c>
+      <c r="BB9" s="0" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="BC9" s="0" t="n">
+        <v>3960985633</v>
+      </c>
+      <c r="BD9" s="0" t="n">
+        <v>1577496</v>
+      </c>
+      <c r="BE9" s="0" t="n">
+        <v>1928703</v>
+      </c>
+      <c r="BF9" s="0" t="n">
+        <v>2032827</v>
+      </c>
+      <c r="BG9" s="0" t="n">
+        <v>88299615</v>
+      </c>
+      <c r="BH9" s="0" t="n">
+        <v>52598607</v>
+      </c>
+      <c r="BI9" s="0" t="n">
+        <v>25985231</v>
+      </c>
+      <c r="BJ9" s="0" t="n">
+        <v>15597804</v>
+      </c>
+      <c r="BK9" s="0" t="n">
+        <v>7154801</v>
+      </c>
+      <c r="BL9" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM9" s="0" t="n">
+        <v>3960985632</v>
+      </c>
+      <c r="BN9" s="0" t="n">
+        <v>101181031</v>
+      </c>
+      <c r="BO9" s="0" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP9" s="0" t="n">
+        <v>64.14</v>
+      </c>
+      <c r="BQ9" s="0" t="n">
+        <v>40130473</v>
+      </c>
+      <c r="BR9" s="0" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BS9" s="0" t="n">
+        <v>20.81</v>
+      </c>
+      <c r="BT9" s="0" t="n">
+        <v>32810773</v>
+      </c>
+      <c r="BU9" s="0" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BV9" s="0" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="BW9" s="0" t="n">
+        <v>1297806819</v>
+      </c>
+      <c r="BX9" s="0" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="BY9" s="0" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="BZ9" s="0" t="n">
+        <v>583994389</v>
+      </c>
+      <c r="CA9" s="0" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="CB9" s="0" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="CC9" s="0" t="n">
+        <v>410217555</v>
+      </c>
+      <c r="CD9" s="0" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="CE9" s="0" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="CF9" s="0" t="n">
+        <v>1187916270</v>
+      </c>
+      <c r="CG9" s="0" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="CH9" s="0" t="n">
+        <v>76.16</v>
+      </c>
+      <c r="CI9" s="0" t="n">
+        <v>306928205</v>
+      </c>
+      <c r="CJ9" s="0" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="CK9" s="0" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="CL9" s="0" t="n">
+        <v>117</v>
+      </c>
+      <c r="CM9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN9" s="0" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="CO9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR9" s="0" t="n">
+        <v>44.56</v>
+      </c>
+      <c r="CS9" s="0" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="CT9" s="0" t="n">
+        <v>177103739</v>
+      </c>
+      <c r="CU9" s="0" t="n">
+        <v>18071347</v>
+      </c>
+      <c r="CV9" s="0" t="n">
+        <v>90.74</v>
+      </c>
+      <c r="CW9" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="CX9" s="0" t="n">
+        <v>93.69</v>
+      </c>
+      <c r="CY9" s="0" t="n">
+        <v>11.67</v>
       </c>
     </row>
     <row r="1048574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="73">
+  <mergeCells count="74">
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:B3"/>
     <mergeCell ref="C1:C3"/>
@@ -2434,27 +2774,27 @@
     <mergeCell ref="E1:E3"/>
     <mergeCell ref="F1:F3"/>
     <mergeCell ref="G1:G3"/>
-    <mergeCell ref="H1:Q1"/>
-    <mergeCell ref="R1:Y1"/>
-    <mergeCell ref="Z1:AG1"/>
-    <mergeCell ref="AH1:AV1"/>
-    <mergeCell ref="AW1:BB1"/>
-    <mergeCell ref="BC1:BK1"/>
-    <mergeCell ref="BL1:CP1"/>
-    <mergeCell ref="CQ1:CR1"/>
-    <mergeCell ref="CS1:CX1"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:Q2"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="S2:Y2"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="AA2:AG2"/>
-    <mergeCell ref="AH2:AH3"/>
+    <mergeCell ref="H1:H3"/>
+    <mergeCell ref="I1:R1"/>
+    <mergeCell ref="S1:Z1"/>
+    <mergeCell ref="AA1:AH1"/>
+    <mergeCell ref="AI1:AW1"/>
+    <mergeCell ref="AX1:BC1"/>
+    <mergeCell ref="BD1:BL1"/>
+    <mergeCell ref="BM1:CQ1"/>
+    <mergeCell ref="CR1:CS1"/>
+    <mergeCell ref="CT1:CY1"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:R2"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="T2:Z2"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="AB2:AH2"/>
     <mergeCell ref="AI2:AI3"/>
-    <mergeCell ref="AJ2:AV2"/>
-    <mergeCell ref="AW2:AW3"/>
-    <mergeCell ref="AX2:BB2"/>
-    <mergeCell ref="BC2:BC3"/>
+    <mergeCell ref="AJ2:AJ3"/>
+    <mergeCell ref="AK2:AW2"/>
+    <mergeCell ref="AX2:AX3"/>
+    <mergeCell ref="AY2:BC2"/>
     <mergeCell ref="BD2:BD3"/>
     <mergeCell ref="BE2:BE3"/>
     <mergeCell ref="BF2:BF3"/>
@@ -2494,12 +2834,13 @@
     <mergeCell ref="CN2:CN3"/>
     <mergeCell ref="CO2:CO3"/>
     <mergeCell ref="CP2:CP3"/>
-    <mergeCell ref="CS2:CS3"/>
+    <mergeCell ref="CQ2:CQ3"/>
     <mergeCell ref="CT2:CT3"/>
     <mergeCell ref="CU2:CU3"/>
     <mergeCell ref="CV2:CV3"/>
     <mergeCell ref="CW2:CW3"/>
     <mergeCell ref="CX2:CX3"/>
+    <mergeCell ref="CY2:CY3"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/npc/doc/NPC性能评估结果.xlsx
+++ b/npc/doc/NPC性能评估结果.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:CY200"/>
+  <dimension ref="A1:DA200"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.4453125" defaultRowHeight="13.8" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="31.03" customWidth="1" style="13" min="2" max="2"/>
@@ -597,6 +597,11 @@
           <t>cache</t>
         </is>
       </c>
+      <c r="CZ1" s="13" t="inlineStr">
+        <is>
+          <t>microbench(train)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="18" customHeight="1" s="14">
       <c r="I2" s="15" t="inlineStr">
@@ -902,6 +907,16 @@
       <c r="CY2" s="18" t="inlineStr">
         <is>
           <t>AMAT/周期</t>
+        </is>
+      </c>
+      <c r="CZ2" s="13" t="inlineStr">
+        <is>
+          <t>耗时/ms</t>
+        </is>
+      </c>
+      <c r="DA2" s="13" t="inlineStr">
+        <is>
+          <t>得分/Marks</t>
         </is>
       </c>
     </row>
@@ -2993,13 +3008,13 @@
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>5147437270</v>
+        <v>5165656915</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>195177022</v>
+        <v>195190049</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>0.0379</v>
+        <v>0.0378</v>
       </c>
       <c r="F12" s="13" t="n">
         <v>1099.046</v>
@@ -3007,251 +3022,251 @@
       <c r="G12" s="13" t="n">
         <v>19164.502</v>
       </c>
-      <c r="H12" t="n">
-        <v>41653843</v>
+      <c r="H12" s="13" t="n">
+        <v>41528664</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>195177022</v>
+        <v>195190049</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>195177024</v>
+        <v>195190051</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>2884820045</v>
+        <v>2888795371</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>56.04</v>
+        <v>55.92</v>
       </c>
       <c r="N12" s="13" t="n">
-        <v>195177022</v>
+        <v>195190049</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>1872263179</v>
+        <v>1886481444</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>36.37</v>
+        <v>36.52</v>
       </c>
       <c r="R12" s="13" t="n">
-        <v>5147437270</v>
+        <v>5165656915</v>
       </c>
       <c r="S12" s="13" t="n">
-        <v>195177022</v>
+        <v>195190049</v>
       </c>
       <c r="T12" s="13" t="n">
-        <v>3275174091</v>
+        <v>3279175471</v>
       </c>
       <c r="U12" s="13" t="n">
-        <v>63.63</v>
+        <v>63.48</v>
       </c>
       <c r="V12" s="13" t="n">
-        <v>195177022</v>
+        <v>195190049</v>
       </c>
       <c r="W12" s="13" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="X12" s="13" t="n">
-        <v>1677086157</v>
+        <v>1691291395</v>
       </c>
       <c r="Y12" s="13" t="n">
-        <v>32.58</v>
+        <v>32.74</v>
       </c>
       <c r="Z12" s="13" t="n">
-        <v>5147437270</v>
+        <v>5165656915</v>
       </c>
       <c r="AA12" s="13" t="n">
-        <v>195177022</v>
+        <v>195190049</v>
       </c>
       <c r="AB12" s="13" t="n">
-        <v>3470351113</v>
+        <v>3474365520</v>
       </c>
       <c r="AC12" s="13" t="n">
-        <v>67.42</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="AD12" s="13" t="n">
-        <v>195177022</v>
+        <v>195190049</v>
       </c>
       <c r="AE12" s="13" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="AF12" s="13" t="n">
-        <v>1481909135</v>
+        <v>1496101346</v>
       </c>
       <c r="AG12" s="13" t="n">
-        <v>28.79</v>
+        <v>28.96</v>
       </c>
       <c r="AH12" s="13" t="n">
-        <v>5147437270</v>
+        <v>5165656915</v>
       </c>
       <c r="AI12" s="13" t="n">
-        <v>15597900</v>
+        <v>15598861</v>
       </c>
       <c r="AJ12" s="13" t="n">
-        <v>7154889</v>
+        <v>7155587</v>
       </c>
       <c r="AK12" s="13" t="n">
-        <v>3665528135</v>
+        <v>3669555569</v>
       </c>
       <c r="AL12" s="13" t="n">
-        <v>71.20999999999999</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="AM12" s="13" t="n">
-        <v>1002128903</v>
+        <v>1017042433</v>
       </c>
       <c r="AN12" s="13" t="n">
-        <v>19.47</v>
+        <v>19.69</v>
       </c>
       <c r="AO12" s="13" t="n">
-        <v>15597900</v>
+        <v>15598861</v>
       </c>
       <c r="AP12" s="13" t="n">
         <v>0.3</v>
       </c>
       <c r="AQ12" s="13" t="n">
-        <v>261850421</v>
+        <v>261114416</v>
       </c>
       <c r="AR12" s="13" t="n">
-        <v>5.09</v>
+        <v>5.05</v>
       </c>
       <c r="AS12" s="13" t="n">
-        <v>7154889</v>
+        <v>7155587</v>
       </c>
       <c r="AT12" s="13" t="n">
         <v>0.14</v>
       </c>
       <c r="AU12" s="13" t="n">
-        <v>195177022</v>
+        <v>195190049</v>
       </c>
       <c r="AV12" s="13" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="AW12" s="13" t="n">
-        <v>5147437270</v>
+        <v>5165656915</v>
       </c>
       <c r="AX12" s="13" t="n">
-        <v>195177022</v>
+        <v>195190049</v>
       </c>
       <c r="AY12" s="13" t="n">
-        <v>4952260248</v>
+        <v>4970466866</v>
       </c>
       <c r="AZ12" s="13" t="n">
-        <v>96.20999999999999</v>
+        <v>96.22</v>
       </c>
       <c r="BA12" s="13" t="n">
-        <v>195177022</v>
+        <v>195190049</v>
       </c>
       <c r="BB12" s="13" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="BC12" s="13" t="n">
-        <v>5147437270</v>
+        <v>5165656915</v>
       </c>
       <c r="BD12" s="13" t="n">
-        <v>1577512</v>
+        <v>1577650</v>
       </c>
       <c r="BE12" s="13" t="n">
-        <v>1928691</v>
+        <v>1929011</v>
       </c>
       <c r="BF12" s="13" t="n">
-        <v>2032813</v>
+        <v>2033132</v>
       </c>
       <c r="BG12" s="13" t="n">
-        <v>88300317</v>
+        <v>88305113</v>
       </c>
       <c r="BH12" s="13" t="n">
-        <v>52598271</v>
+        <v>52603126</v>
       </c>
       <c r="BI12" s="13" t="n">
-        <v>25986627</v>
+        <v>25987567</v>
       </c>
       <c r="BJ12" s="13" t="n">
-        <v>15597900</v>
+        <v>15598861</v>
       </c>
       <c r="BK12" s="13" t="n">
-        <v>7154889</v>
+        <v>7155587</v>
       </c>
       <c r="BL12" s="13" t="n">
         <v>2</v>
       </c>
       <c r="BM12" s="13" t="n">
-        <v>5147437269</v>
+        <v>5165656914</v>
       </c>
       <c r="BN12" s="13" t="n">
-        <v>140671794</v>
+        <v>140602763</v>
       </c>
       <c r="BO12" s="13" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="BP12" s="13" t="n">
-        <v>89.17</v>
+        <v>89.12</v>
       </c>
       <c r="BQ12" s="13" t="n">
-        <v>53255171</v>
+        <v>53299900</v>
       </c>
       <c r="BR12" s="13" t="n">
         <v>1.03</v>
       </c>
       <c r="BS12" s="13" t="n">
-        <v>27.61</v>
+        <v>27.63</v>
       </c>
       <c r="BT12" s="13" t="n">
-        <v>41955259</v>
+        <v>41972062</v>
       </c>
       <c r="BU12" s="13" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BV12" s="13" t="n">
         <v>20.64</v>
       </c>
       <c r="BW12" s="13" t="n">
-        <v>1614478098</v>
+        <v>1604986614</v>
       </c>
       <c r="BX12" s="13" t="n">
-        <v>31.36</v>
+        <v>31.07</v>
       </c>
       <c r="BY12" s="13" t="n">
-        <v>18.28</v>
+        <v>18.18</v>
       </c>
       <c r="BZ12" s="13" t="n">
-        <v>690725338</v>
+        <v>689754385</v>
       </c>
       <c r="CA12" s="13" t="n">
-        <v>13.42</v>
+        <v>13.35</v>
       </c>
       <c r="CB12" s="13" t="n">
-        <v>13.13</v>
+        <v>13.11</v>
       </c>
       <c r="CC12" s="13" t="n">
-        <v>519119497</v>
+        <v>586707840</v>
       </c>
       <c r="CD12" s="13" t="n">
-        <v>10.09</v>
+        <v>11.36</v>
       </c>
       <c r="CE12" s="13" t="n">
-        <v>19.98</v>
+        <v>22.58</v>
       </c>
       <c r="CF12" s="13" t="n">
-        <v>1671060571</v>
+        <v>1630678390</v>
       </c>
       <c r="CG12" s="13" t="n">
-        <v>32.46</v>
+        <v>31.57</v>
       </c>
       <c r="CH12" s="13" t="n">
-        <v>107.13</v>
+        <v>104.54</v>
       </c>
       <c r="CI12" s="13" t="n">
-        <v>416171409</v>
+        <v>417654828</v>
       </c>
       <c r="CJ12" s="13" t="n">
         <v>8.09</v>
       </c>
       <c r="CK12" s="13" t="n">
-        <v>58.17</v>
+        <v>58.37</v>
       </c>
       <c r="CL12" s="13" t="n">
         <v>132</v>
@@ -3272,16 +3287,16 @@
         <v>0</v>
       </c>
       <c r="CR12" s="13" t="n">
-        <v>64.25</v>
+        <v>65.2</v>
       </c>
       <c r="CS12" s="13" t="n">
-        <v>36.6</v>
+        <v>36.49</v>
       </c>
       <c r="CT12" s="13" t="n">
-        <v>177104907</v>
+        <v>177122300</v>
       </c>
       <c r="CU12" s="13" t="n">
-        <v>18072115</v>
+        <v>18067749</v>
       </c>
       <c r="CV12" s="13" t="n">
         <v>90.73999999999999</v>
@@ -3290,10 +3305,16 @@
         <v>3</v>
       </c>
       <c r="CX12" s="13" t="n">
-        <v>138.03</v>
+        <v>138.28</v>
       </c>
       <c r="CY12" s="13" t="n">
-        <v>15.78</v>
+        <v>15.8</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>4320741.033</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="13.8" customHeight="1" s="14">
@@ -3962,7 +3983,7 @@
     <row r="1048575" ht="12.75" customHeight="1" s="14"/>
     <row r="1048576" ht="12.75" customHeight="1" s="14"/>
   </sheetData>
-  <mergeCells count="74">
+  <mergeCells count="75">
     <mergeCell ref="BI2:BI3"/>
     <mergeCell ref="BU2:BU3"/>
     <mergeCell ref="CB2:CB3"/>
@@ -4037,6 +4058,7 @@
     <mergeCell ref="AB2:AH2"/>
     <mergeCell ref="AJ2:AJ3"/>
     <mergeCell ref="I2:I3"/>
+    <mergeCell ref="CZ1:DA1"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
